--- a/docs/basic-v0.1.xlsx
+++ b/docs/basic-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF5811D-3125-4C92-854F-EA7A035F760B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D962F08B-024C-4D67-A3A1-EEE168E751A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="324">
   <si>
     <t>チーム名:個人開発</t>
   </si>
@@ -461,6 +461,592 @@
   </si>
   <si>
     <t>設定の画面に、裏の仕事ごとの「最後に動いた時刻」を並べる(Outlook・Gmail・Google カレンダー・通知・Claude・予備)。決まった間隔より遅れているものは赤く出す。タスクスケジューラに本体が登録されているかも出す(schtasks で確かめる)。どれかが赤いときは、トップの2段目④にも「止まっている仕事があります」と出す</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Q23</t>
+  </si>
+  <si>
+    <t>基本 画面項目(S1-3)</t>
+  </si>
+  <si>
+    <t>作業記録を手でつけるか、全自動にするか。作業時間の合計を見られるようにするか</t>
+  </si>
+  <si>
+    <t>全自動にする。1分ごとに、前に出ている窓の名前(画面の中身は見ない)から入れ物を判断して記録する(例:VS Code の fx-practice のフォルダ → fx-practice、学習サイトの授業のページ → その授業、Word の卒論のファイル → 卒論)。同じ入れ物が続く間を1つの記録にし、判断できない時間は記録しない。初めて見た窓は連絡の画面で「どの入れ物?」と聞き、答え(窓の名前の決まり)を覚える。窓の名前そのものは、答えを待つ間だけ data/ に置き、答えたら消す。手での [開始] [止める] [切り替え] も残す(自動の記録を手で直したいとき)。入れ物の中の画面に「今週 ○時間/全部で ○時間」を出す。要件定義書 F4 などを書き直す(1.03)</t>
+  </si>
+  <si>
+    <t>Q24</t>
+  </si>
+  <si>
+    <t>基本 Q23</t>
+  </si>
+  <si>
+    <t>自動の記録で「どのタスクの作業か」をどう扱うか(手つかずの通知 F8・「終わった?」F18 ③ との関係)</t>
+  </si>
+  <si>
+    <t>自動の記録は入れ物までにする。手つかずの通知(F8)は、その入れ物に自動の記録があれば「手をつけた」とみなす。「終わった?」(F18 ③)は、入れ物の自動の記録が15分以上続いて終わったとき、「○○で終わったタスクはある?」とその入れ物のタスクを並べて聞く(1つの入れ物につき1日1回。出し方は Q5 と同じ1段目)。タスクごとに記録したいときは、手で [開始] を押してタスクを選ぶ(手の記録は Q15 のとおり)。2時間続いたときの通知(切り替え忘れ)と、PC が眠ったあとの「再開しますか?」は、手の記録だけに出す(自動の記録は窓を見て勝手に切り替わるため)</t>
+  </si>
+  <si>
+    <t>Q25</t>
+  </si>
+  <si>
+    <t>手で作業を開始・切り替えるときの押し方</t>
+  </si>
+  <si>
+    <t>手での [開始] [切り替え] [止める] は置かない。記録はすべて自動にする。1段目(S1-3)には、自動の記録(「自動: fx-practice 0:42」)を出すだけにする。自動の記録がまちがっていたときは、入れ物の中の画面で、あとから直す・消す(F5)。これにより、Q15 と Q23・Q24 の「手の記録」の部分は使わなくなる(「終わった?」は Q24 の入れ物の単位だけ。2時間続いたときの通知と「再開しますか?」はなくす)。要件定義書 F4・F8・F18 と非機能要件の「切り替えは2クリック以内」を書き直す(1.03)</t>
+  </si>
+  <si>
+    <t>S1-1</t>
+  </si>
+  <si>
+    <t>トップ/一番上</t>
+  </si>
+  <si>
+    <t>全体のゲージ</t>
+  </si>
+  <si>
+    <t>細いバー1本と「○% 完了」。押すと小窓が開き、全体・種類ごと・今日か今週にタスクがある入れ物のゲージを並べる(F6)</t>
+  </si>
+  <si>
+    <t>S1-2</t>
+  </si>
+  <si>
+    <t>トップ/S1-1 の下</t>
+  </si>
+  <si>
+    <t>「トップに出す」入れ物のゲージ</t>
+  </si>
+  <si>
+    <t>「トップに出す」を選んだ入れ物ごとに1本。タスクが0件なら「タスクなし」(F6)</t>
+  </si>
+  <si>
+    <t>S1-3</t>
+  </si>
+  <si>
+    <t>トップ/1段目</t>
+  </si>
+  <si>
+    <t>記録中</t>
+  </si>
+  <si>
+    <t>自動の記録の入れ物名と経過時間(例:「自動: fx-practice 0:42」)。記録がないときは「記録なし」。手で押すボタンは置かない(Q25)。入れ物の記録が終わったときの「○○で終わったタスクはある?」もここに出す(Q5・Q24)</t>
+  </si>
+  <si>
+    <t>S1-4</t>
+  </si>
+  <si>
+    <t>トップ/2段目</t>
+  </si>
+  <si>
+    <t>お知らせ</t>
+  </si>
+  <si>
+    <t>あるときだけ出す。①再開の確認はなし(Q25)②PC の電源が切れていた間の通知 ③学期の終わりの米印 ④読めなかった・つながらなかった・止まっている仕事(Q6・Q19)⑤読み込み中 ⑥カレンダーに書かなかった予定 ⑦新しい連絡 ○件 ⑧終わっていそう ○件 ⑨未分類 ○件(F3)</t>
+  </si>
+  <si>
+    <t>S1-5</t>
+  </si>
+  <si>
+    <t>トップ/3段目</t>
+  </si>
+  <si>
+    <t>期限切れ</t>
+  </si>
+  <si>
+    <t>締切を過ぎた未完了のタスクを、色を変えてまとめる。完了にするか締切を変えるまで残る(F3)</t>
+  </si>
+  <si>
+    <t>S1-6</t>
+  </si>
+  <si>
+    <t>トップ/3段目の下</t>
+  </si>
+  <si>
+    <t>1行入力</t>
+  </si>
+  <si>
+    <t>入力欄1つと、その横の「AI」トグル(初めはオフ=決まった書き方で読む)。Enter でタスクにする(F17・Q3・Q10)</t>
+  </si>
+  <si>
+    <t>S1-7</t>
+  </si>
+  <si>
+    <t>トップ/S1-6 の下</t>
+  </si>
+  <si>
+    <t>S1-8</t>
+  </si>
+  <si>
+    <t>トップ/S1-7 の下</t>
+  </si>
+  <si>
+    <t>今日</t>
+  </si>
+  <si>
+    <t>今日が締切のタスクを締切順に。その下に、着手日で上がったタスクを「今日から始める」印つきで出す(F3・F16・Q3)</t>
+  </si>
+  <si>
+    <t>S1-9</t>
+  </si>
+  <si>
+    <t>トップ/S1-8 の下</t>
+  </si>
+  <si>
+    <t>今週</t>
+  </si>
+  <si>
+    <t>S1-10</t>
+  </si>
+  <si>
+    <t>トップ/S1-9 の下</t>
+  </si>
+  <si>
+    <t>締切なし</t>
+  </si>
+  <si>
+    <t>締切のないタスクを登録が古い順に(F3)</t>
+  </si>
+  <si>
+    <t>S1-8〜10 共通</t>
+  </si>
+  <si>
+    <t>タスクの行</t>
+  </si>
+  <si>
+    <t>ラベル・名前・締切・印</t>
+  </si>
+  <si>
+    <t>S1-11</t>
+  </si>
+  <si>
+    <t>明日から6日後までが締切のタスクを締切順に(今日を入れて7日間。Q4)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの行の操作</t>
+  </si>
+  <si>
+    <t>完了のチェック・行を押す</t>
+  </si>
+  <si>
+    <t>行の左の丸いチェックを押すと完了。5秒間だけ「元に戻す」を出す。行のほかの場所を押すと、入れ物の中の画面でそのタスクを開く(画面2)</t>
+  </si>
+  <si>
+    <t>今日の時間・明日の時間</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>授業と、時刻の決まった予定だけを時刻順に出す。「今日」の下に「明日」も同じ形で出す(本人の希望で追加)。タスクの締切は出さない(F3・F10・F19)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Q26</t>
+  </si>
+  <si>
+    <t>基本 画面項目</t>
+  </si>
+  <si>
+    <t>workbench の窓の大きさ(横長か、細長いか)</t>
+  </si>
+  <si>
+    <t>窓の幅に合わせて自動で変わる。広いときは、左に画面切り替えの縦の帯、真ん中にゲージ・記録中・期限切れ・1行入力・今日・今週・締切なし、右にお知らせと今日・明日の時間。狭いときは、全部を1列に縦に並べ、画面切り替えは下の帯。部品と順番はどちらも同じ。切り替わる幅は UI 試作で決める。構想設計書の「画面の一番下に5つのボタン」を直す</t>
+  </si>
+  <si>
+    <t>全画面/広いときは左、狭いときは一番下</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>画面切り替えの帯</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>トップ・予定・連絡・入れ物・設定の5つのボタン。広いときは左の縦の帯、狭いときは下の帯(Q26)。新しい連絡があるときは「連絡」に青い点(構想設計)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Q27</t>
+  </si>
+  <si>
+    <t>基本 画面項目(本人の希望)</t>
+  </si>
+  <si>
+    <t>授業で使うサイトやツールに、トップからワンクリックで飛べるようにする。リンクをどこに出すか</t>
+  </si>
+  <si>
+    <t>入れ物の中の画面で、入れ物ごとにリンク(名前と URL、または PC のアプリ・フォルダ)を登録する。トップのゲージのすぐ下に「今日のリンク」の行を作り、今日の時間割にある授業の入れ物のリンクを、授業の時刻順に並べる。入れ物ごとに「いつもトップに出す」を選ぶと、毎日そのリンクも並べる。開くのは自分が押したときだけ(X6)。要件定義書に新しい機能として足す(1.03)</t>
+  </si>
+  <si>
+    <t>S1-12</t>
+  </si>
+  <si>
+    <t>トップ/S1-2 の下</t>
+  </si>
+  <si>
+    <t>今日のリンク</t>
+  </si>
+  <si>
+    <t>今日の時間割にある授業の入れ物に登録したリンクを、授業の時刻順にボタンで並べる。「いつもトップに出す」を選んだ入れ物のリンクも並べる。押すとサイトやアプリが開く。リンクがなければ行ごと出さない(Q27)</t>
+  </si>
+  <si>
+    <t>S2-1</t>
+  </si>
+  <si>
+    <t>スケジュール/一番上</t>
+  </si>
+  <si>
+    <t>切り替え・月の移動・[+ 予定]</t>
+  </si>
+  <si>
+    <t>S2-1a</t>
+  </si>
+  <si>
+    <t>スケジュール/小窓</t>
+  </si>
+  <si>
+    <t>予定を足す小窓</t>
+  </si>
+  <si>
+    <t>S2-2</t>
+  </si>
+  <si>
+    <t>スケジュール/S2-1 の下</t>
+  </si>
+  <si>
+    <t>シフト表の写真を落とす場所</t>
+  </si>
+  <si>
+    <t>写真をここに落とすと Claude が読み取り、結果を小窓に出す(F14)</t>
+  </si>
+  <si>
+    <t>S2-3</t>
+  </si>
+  <si>
+    <t>スケジュール/S2-2 の下</t>
+  </si>
+  <si>
+    <t>Google に書けなかった予定</t>
+  </si>
+  <si>
+    <t>書けなかった予定があるときだけ出す帯。押すと一覧が開き、予定ごとに理由(つながらなかった/重なる予定がある)と [もう一度書く] ボタンを出す。重なる予定のときは [それでも書く] [書かない] も出す。つながったら自動でももう一度書く(F13・本人の希望で [もう一度書く] を追加)</t>
+  </si>
+  <si>
+    <t>S2-4</t>
+  </si>
+  <si>
+    <t>スケジュール/真ん中</t>
+  </si>
+  <si>
+    <t>日付ごとの一覧</t>
+  </si>
+  <si>
+    <t>日付ごとに、授業・予定・タスクの締切を時刻順に並べる。入れ物のラベルは種類の色。締切の行には完了の丸(トップと同じ)。workbench が書いた締切の予定は、タスクとして1回だけ出す。招待された予定には印をつける(印の形は UI 試作)(F19)</t>
+  </si>
+  <si>
+    <t>S2-4m</t>
+  </si>
+  <si>
+    <t>スケジュール/月の画面</t>
+  </si>
+  <si>
+    <t>月のマス目</t>
+  </si>
+  <si>
+    <t>S2-5</t>
+  </si>
+  <si>
+    <t>予定を押したときの小窓</t>
+  </si>
+  <si>
+    <t>直す・消す(消す前に確認)・入れ物を選ぶ。招待された予定は、予定ごとのトグルで編集を許したときだけ直せる。主催者が変更を許していなければ「主催者が変更を許可していないため、直せませんでした」と出す(F19)</t>
+  </si>
+  <si>
+    <t>「一覧」と「月」の切り替え(ふだんは一覧)、前後の月への移動、[+ 予定]。[+ 予定] を押すと、予定を足す小窓を開く(画面5)(F19)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>名前・日付・始まりと終わりの時刻・入れ物(なしでもよい)を入れて [保存]。月の画面の日付の小窓から [+ この日に予定を足す] で開いたときは、その日付が入っている。保存するとその場で Google カレンダーにも書く(F19・画面5・画面6)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>予定を点で出す。点の色は入れ物の種類の色、入れ物なしは灰色(Q16)。日付を押すと、その日の一覧を小窓で出す。小窓の一番上に [+ この日に予定を足す] を置く(画面6)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>S3-1</t>
+  </si>
+  <si>
+    <t>連絡/左(狭いときは上の横並び)</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>上から「workbench から」・授業・奨学金・試合のチケット・企業・アルバイト・自動で完了・その他(たたんだ状態)。分類ごとに新しい件数を出す。連絡の画面を開いたら、トップの「新しい連絡 ○件」と下の帯の青い点を消す(メールの既読には触らない)(F9・画面7)</t>
+  </si>
+  <si>
+    <t>S3-2</t>
+  </si>
+  <si>
+    <t>連絡/右(「workbench から」を選んだとき)</t>
+  </si>
+  <si>
+    <t>質問とお知らせ</t>
+  </si>
+  <si>
+    <t>答えが必要な質問:「VS Code で開いている「○○」は、どの入れ物の作業ですか?」[入れ物を選ぶ][記録しない](Q23)/「どのバイト先?」(Q21)/「候補日あり」と候補日のボタン(Q22)。お知らせ:「○○を自動で完了にしました」ともとになったもの(Q14)。答えた質問は一覧から消える</t>
+  </si>
+  <si>
+    <t>S3-3</t>
+  </si>
+  <si>
+    <t>連絡/右(メールの分類を選んだとき)</t>
+  </si>
+  <si>
+    <t>メールの一覧</t>
+  </si>
+  <si>
+    <t>件名・差出人・日付を新しい順に。新しいものには印。押すと本文を開く(F9・F11・F20)</t>
+  </si>
+  <si>
+    <t>S3-4</t>
+  </si>
+  <si>
+    <t>連絡/メールを開いたとき</t>
+  </si>
+  <si>
+    <t>メールの本文</t>
+  </si>
+  <si>
+    <t>本文(90日で本文だけ消える)/本文の中のリンク(押すと開く。X6)/[入れ物を選び直す](選び直しを覚える)/[この差出人は取り込まない](Q20)/このメールから自動で入ったタスクや予定へのつながり(1回の操作で消せる)(F9・F11・F20)</t>
+  </si>
+  <si>
+    <t>S3-5</t>
+  </si>
+  <si>
+    <t>連絡/右(「自動で完了」を選んだとき)</t>
+  </si>
+  <si>
+    <t>自動で完了の欄</t>
+  </si>
+  <si>
+    <t>自動で完了にしたタスクを新しい順に。行ごとに [戻す](未完了に戻し、カレンダーの「済」を消す)。古いものは「もっと見る」でたどる(Q14)</t>
+  </si>
+  <si>
+    <t>S4-1</t>
+  </si>
+  <si>
+    <t>入れ物の一覧/一番上</t>
+  </si>
+  <si>
+    <t>[+ 入れ物]・全体の進み具合</t>
+  </si>
+  <si>
+    <t>[+ 入れ物] で入れ物を足す(種類を選ぶ)。全体の「○% 完了」を出す(F1・F6)</t>
+  </si>
+  <si>
+    <t>S4-2</t>
+  </si>
+  <si>
+    <t>入れ物の一覧/S4-1 の下</t>
+  </si>
+  <si>
+    <t>未分類の帯</t>
+  </si>
+  <si>
+    <t>未分類のタスクがあるときだけ「未分類 ○件 ― 入れ物を選んでください」と出す。押すと仕分けの一覧を開く(F1・F2)</t>
+  </si>
+  <si>
+    <t>S4-3</t>
+  </si>
+  <si>
+    <t>入れ物の一覧/真ん中</t>
+  </si>
+  <si>
+    <t>種類ごとの入れ物</t>
+  </si>
+  <si>
+    <t>種類ごとに、種類の色・名前・種類ごとの進み具合を出し、その下に入れ物の名前とゲージ(タスク0件は「タスクなし」)を並べる。種類の中は、締切の近いタスクがある入れ物から順に、締切のあるタスクがない入れ物は最後に名前順(画面8)。入れ物を押すと入れ物の中の画面を開く(F1・F6)</t>
+  </si>
+  <si>
+    <t>S4-4</t>
+  </si>
+  <si>
+    <t>入れ物の一覧/一番下</t>
+  </si>
+  <si>
+    <t>終了した入れ物</t>
+  </si>
+  <si>
+    <t>たたんだ状態。押すと開き、入れ物ごとに [戻す] がある(F1)</t>
+  </si>
+  <si>
+    <t>S5-1</t>
+  </si>
+  <si>
+    <t>入れ物の中/一番上(いつも出す)</t>
+  </si>
+  <si>
+    <t>入れ物の名前と進み具合</t>
+  </si>
+  <si>
+    <t>[&lt; 入れ物の一覧]/入れ物の名前と種類/説明(開発は README の段落か自分の一言。F15)/工程(spec-excel の工程か、自分で選んだ状態。F15)/「○% 完了」とゲージ(F6)/「今週 ○時間/全部で ○時間」(Q23・画面8-1)</t>
+  </si>
+  <si>
+    <t>S5-2</t>
+  </si>
+  <si>
+    <t>入れ物の中/S5-1 の下</t>
+  </si>
+  <si>
+    <t>見出し</t>
+  </si>
+  <si>
+    <t>「タスク」「記録」「リンク」「設定」の4つで切り替える。開いたときは「タスク」(画面9)</t>
+  </si>
+  <si>
+    <t>S5-3</t>
+  </si>
+  <si>
+    <t>入れ物の中/タスク</t>
+  </si>
+  <si>
+    <t>タスクの一覧</t>
+  </si>
+  <si>
+    <t>未完了を締切順に、完了したものはその下に。行の左の丸で完了(トップと同じ)。行を押すと直す・消す(消す前に確認)。印(メールから自動で入った・AI)はトップと同じ(F2)</t>
+  </si>
+  <si>
+    <t>S5-4</t>
+  </si>
+  <si>
+    <t>入れ物の中/記録</t>
+  </si>
+  <si>
+    <t>作業記録</t>
+  </si>
+  <si>
+    <t>自動の記録と git のコミットを日付ごとに並べる。記録の開始・終了の時刻と内容を直す・足す・消す(消す前に確認。git から入ったものは消したら戻ってこない)(F5・F7)</t>
+  </si>
+  <si>
+    <t>S5-5</t>
+  </si>
+  <si>
+    <t>入れ物の中/リンク</t>
+  </si>
+  <si>
+    <t>リンク</t>
+  </si>
+  <si>
+    <t>名前と URL、または PC のアプリ・フォルダを足す・直す・消す。「いつもトップに出す」のトグル(Q27)</t>
+  </si>
+  <si>
+    <t>S5-6</t>
+  </si>
+  <si>
+    <t>入れ物の中/設定</t>
+  </si>
+  <si>
+    <t>入れ物の設定</t>
+  </si>
+  <si>
+    <t>名前/種類(あとから変えられる)/「トップに出す」(F6)/リポジトリの場所(F7)/企業のメールアドレスの @ から後ろ(就活の入れ物だけ。F11)/開発の状態(spec-excel の工程がないとき。F15)/[終了にする](F1)/[消す](中身が空のときだけ。F1)</t>
+  </si>
+  <si>
+    <t>S5-3a</t>
+  </si>
+  <si>
+    <t>入れ物の中/タスク の一番上</t>
+  </si>
+  <si>
+    <t>タスクを足す欄</t>
+  </si>
+  <si>
+    <t>トップの1行入力と同じ書き方の欄(例:「金 23:59 第10回課題」)。入れ物はこの入れ物に決まっている。横の [くわしく] を押すと小窓が開き、名前・締切(日付と時刻)・毎週の繰り返し・着手日(F16)を入れられる(F2・画面10)</t>
+  </si>
+  <si>
+    <t>S6-0</t>
+  </si>
+  <si>
+    <t>設定/一番上</t>
+  </si>
+  <si>
+    <t>目次</t>
+  </si>
+  <si>
+    <t>下の見出しへ飛ぶ目次。設定は1ページに縦に並べる(画面11)</t>
+  </si>
+  <si>
+    <t>S6-1</t>
+  </si>
+  <si>
+    <t>設定/種類</t>
+  </si>
+  <si>
+    <t>種類</t>
+  </si>
+  <si>
+    <t>種類を足す・名前と色を変える(灰色は選べない)・消す(中に入れ物がない種類だけ。初めの3つは消せない)。種類ごとに「同じ締切のとき先に並べる」「締切なしに手つかずの通知を出す」のトグル(F1・Q2)</t>
+  </si>
+  <si>
+    <t>S6-2</t>
+  </si>
+  <si>
+    <t>設定/メールと連絡</t>
+  </si>
+  <si>
+    <t>メールと連絡</t>
+  </si>
+  <si>
+    <t>大学のアドレスの形(@ から後ろ。data/ に置く。F9)/止めた差出人の一覧と [外す](Q20)/バイト先の一覧(名前と、覚えた中継アドレスか @ から後ろ。足す・直す・消す。F20・Q21)</t>
+  </si>
+  <si>
+    <t>S6-3</t>
+  </si>
+  <si>
+    <t>設定/Google</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Google の許可の状態と [許可し直す](F11〜F13)</t>
+  </si>
+  <si>
+    <t>S6-4</t>
+  </si>
+  <si>
+    <t>設定/作業記録</t>
+  </si>
+  <si>
+    <t>覚えたアプリの画面の名前と入れ物の組み合わせの一覧(「記録しない」も含む)。直す・消す(Q23)</t>
+  </si>
+  <si>
+    <t>S6-5</t>
+  </si>
+  <si>
+    <t>設定/大学</t>
+  </si>
+  <si>
+    <t>大学</t>
+  </si>
+  <si>
+    <t>学期の終わりの日(Claude が学年暦を読んで入れる。直せる。Q7)/シフト表での自分の名前(F14)</t>
+  </si>
+  <si>
+    <t>S6-6</t>
+  </si>
+  <si>
+    <t>設定/本体の様子</t>
+  </si>
+  <si>
+    <t>本体の様子</t>
+  </si>
+  <si>
+    <t>裏の仕事ごと(Outlook・Gmail・Google カレンダー・通知・Claude・予備・作業記録)の最後に動いた時刻。決まった間隔より遅れているものは赤。タスクスケジューラに登録されているか(Q19)</t>
+  </si>
+  <si>
+    <t>入れ物名のラベル(種類の色。未分類は灰色)/タスク名/締切(時刻があれば時刻も)/印:「メールから自動で入った」「入れ物を選んで」「AI」(Claude が読み取った。Q18)、画面での通知の印「明日が締切」「手つかず」「着手日を過ぎた」(Q5)(F1・F2・F3・F8)</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -606,7 +1192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -639,6 +1225,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1259,7 +1848,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1580,31 +2169,101 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="108">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="17" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="108">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="17" t="s">
         <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="121.5">
+      <c r="A28" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="108">
+      <c r="A29" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="94.5">
+      <c r="A30" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="67.5">
+      <c r="A31" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="67.5">
+      <c r="A32" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -1622,7 +2281,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1660,6 +2319,622 @@
       </c>
       <c r="D5" s="6" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27">
+      <c r="A6" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27">
+      <c r="A7" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="40.5">
+      <c r="A8" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="54">
+      <c r="A9" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27">
+      <c r="A10" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27">
+      <c r="A11" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="27">
+      <c r="A12" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27">
+      <c r="A13" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="40.5">
+      <c r="A16" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="27">
+      <c r="A17" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="27">
+      <c r="A18" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="40.5">
+      <c r="A19" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="27">
+      <c r="A20" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="40.5">
+      <c r="A21" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="27">
+      <c r="A22" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="54">
+      <c r="A23" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="40.5">
+      <c r="A24" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="27">
+      <c r="A25" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="40.5">
+      <c r="A26" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="40.5">
+      <c r="A27" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="54">
+      <c r="A28" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="27">
+      <c r="A29" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="40.5">
+      <c r="A30" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="27">
+      <c r="A31" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="27">
+      <c r="A32" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="27">
+      <c r="A33" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="54">
+      <c r="A34" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="40.5">
+      <c r="A36" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="27">
+      <c r="A38" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="27">
+      <c r="A39" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="27">
+      <c r="A40" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="40.5">
+      <c r="A41" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="40.5">
+      <c r="A42" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="40.5">
+      <c r="A44" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="40.5">
+      <c r="A45" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="27">
+      <c r="A47" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="27">
+      <c r="A48" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="40.5">
+      <c r="A49" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/docs/basic-v0.1.xlsx
+++ b/docs/basic-v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Workspace\02_開発\workbench\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D962F08B-024C-4D67-A3A1-EEE168E751A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84825A76-8C4F-4363-BC12-A77F0E85BE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="708">
   <si>
     <t>チーム名:個人開発</t>
   </si>
@@ -1048,6 +1048,1159 @@
   <si>
     <t>入れ物名のラベル(種類の色。未分類は灰色)/タスク名/締切(時刻があれば時刻も)/印:「メールから自動で入った」「入れ物を選んで」「AI」(Claude が読み取った。Q18)、画面での通知の印「明日が締切」「手つかず」「着手日を過ぎた」(Q5)(F1・F2・F3・F8)</t>
     <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>kinds 種類</t>
+  </si>
+  <si>
+    <t>【表】入れ物の種類(F1)。ずっと残す</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>整数</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>番号</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>文字</t>
+  </si>
+  <si>
+    <t>種類の名前</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>色(灰色は不可)</t>
+  </si>
+  <si>
+    <t>sort_first</t>
+  </si>
+  <si>
+    <t>真偽</t>
+  </si>
+  <si>
+    <t>同じ締切のとき先に並べるか(Q2:新しい種類はオフ)</t>
+  </si>
+  <si>
+    <t>notify_untouched</t>
+  </si>
+  <si>
+    <t>締切なしに手つかずの通知を出すか(Q2:新しい種類はオン)</t>
+  </si>
+  <si>
+    <t>builtin</t>
+  </si>
+  <si>
+    <t>初めからある3つ(大学・就活・開発)。消せない</t>
+  </si>
+  <si>
+    <t>containers 入れ物</t>
+  </si>
+  <si>
+    <t>【表】授業・企業・アプリなど(F1)。消さずに終了にする</t>
+  </si>
+  <si>
+    <t>kind_id</t>
+  </si>
+  <si>
+    <t>種類。未分類の入れ物だけ空</t>
+  </si>
+  <si>
+    <t>is_unsorted</t>
+  </si>
+  <si>
+    <t>特別な入れ物「未分類」か(1つだけ)</t>
+  </si>
+  <si>
+    <t>名前</t>
+  </si>
+  <si>
+    <t>ended</t>
+  </si>
+  <si>
+    <t>終了したか</t>
+  </si>
+  <si>
+    <t>show_on_top</t>
+  </si>
+  <si>
+    <t>トップにゲージを出すか(F6)</t>
+  </si>
+  <si>
+    <t>auto_source</t>
+  </si>
+  <si>
+    <t>自動で作ったときのもと(時間割・奨学金・試合のチケット・企業)。種類を移しても同じ入れ物として扱う(Q1)</t>
+  </si>
+  <si>
+    <t>repo_path</t>
+  </si>
+  <si>
+    <t>git のリポジトリの場所(F7)</t>
+  </si>
+  <si>
+    <t>company_domain</t>
+  </si>
+  <si>
+    <t>企業のメールアドレスの @ から後ろ(F11)</t>
+  </si>
+  <si>
+    <t>own_description</t>
+  </si>
+  <si>
+    <t>開発の説明の自分の一言(F15)</t>
+  </si>
+  <si>
+    <t>dev_state</t>
+  </si>
+  <si>
+    <t>自分で選んだ状態(アイデア/作成中/動いている/休止。F15)</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>日時</t>
+  </si>
+  <si>
+    <t>作った日時</t>
+  </si>
+  <si>
+    <t>tasks タスク</t>
+  </si>
+  <si>
+    <t>【表】締切つきのやること(F2)。ずっと残す</t>
+  </si>
+  <si>
+    <t>container_id</t>
+  </si>
+  <si>
+    <t>入れ物</t>
+  </si>
+  <si>
+    <t>due_date</t>
+  </si>
+  <si>
+    <t>締切の日付(なしでもよい)</t>
+  </si>
+  <si>
+    <t>due_time</t>
+  </si>
+  <si>
+    <t>時刻</t>
+  </si>
+  <si>
+    <t>締切の時刻(任意)</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>着手日(F16)</t>
+  </si>
+  <si>
+    <t>repeat_weekday</t>
+  </si>
+  <si>
+    <t>毎週の繰り返しの曜日(繰り返しなしは空)</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>完了したか</t>
+  </si>
+  <si>
+    <t>done_at</t>
+  </si>
+  <si>
+    <t>完了した日時</t>
+  </si>
+  <si>
+    <t>auto_done_by</t>
+  </si>
+  <si>
+    <t>自動で完了にした合図(提出受付・Forms・エントリー受付・コミット)。手で完了なら空(F18・Q14)</t>
+  </si>
+  <si>
+    <t>from_message_id</t>
+  </si>
+  <si>
+    <t>メールから自動で入ったとき、もとの連絡(F9)</t>
+  </si>
+  <si>
+    <t>ai_read</t>
+  </si>
+  <si>
+    <t>Claude が読み取ったか(Q18)</t>
+  </si>
+  <si>
+    <t>ai_checked</t>
+  </si>
+  <si>
+    <t>「AI」の札を確かめたか。確かめたら札を消す(Q18)</t>
+  </si>
+  <si>
+    <t>calendar_written</t>
+  </si>
+  <si>
+    <t>Google カレンダーに書いたか(F13・Q8)</t>
+  </si>
+  <si>
+    <t>登録した日時(並び順に使う)</t>
+  </si>
+  <si>
+    <t>work_logs 作業記録</t>
+  </si>
+  <si>
+    <t>【表】全自動の作業記録(F4・Q23)。ずっと残す</t>
+  </si>
+  <si>
+    <t>task_id</t>
+  </si>
+  <si>
+    <t>タスク(自動の記録は空。Q24)</t>
+  </si>
+  <si>
+    <t>started_at</t>
+  </si>
+  <si>
+    <t>始まり</t>
+  </si>
+  <si>
+    <t>ended_at</t>
+  </si>
+  <si>
+    <t>終わり(記録中は空)</t>
+  </si>
+  <si>
+    <t>edited</t>
+  </si>
+  <si>
+    <t>手で直したか(F5)</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>内容(手で書き足した分)</t>
+  </si>
+  <si>
+    <t>commits コミット</t>
+  </si>
+  <si>
+    <t>【表】git から取り込んだコミット(F7)</t>
+  </si>
+  <si>
+    <t>work_log_id</t>
+  </si>
+  <si>
+    <t>くっついた作業記録(なければ点として並べる)</t>
+  </si>
+  <si>
+    <t>hash</t>
+  </si>
+  <si>
+    <t>コミットの番号(同じものを二度取り込まない)</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>メッセージ</t>
+  </si>
+  <si>
+    <t>committed_at</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>消したか。消したものは次の取り込みで戻さない(F5)</t>
+  </si>
+  <si>
+    <t>messages 取り込んだ連絡</t>
+  </si>
+  <si>
+    <t>【表】Outlook と Gmail のメール(F9・F11・F20)</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>Outlook か Gmail</t>
+  </si>
+  <si>
+    <t>external_id</t>
+  </si>
+  <si>
+    <t>もとのメールの番号(同じものを二度取り込まない)</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>授業・奨学金・試合のチケット・企業・アルバイト・その他</t>
+  </si>
+  <si>
+    <t>振り分けた入れ物</t>
+  </si>
+  <si>
+    <t>baito_id</t>
+  </si>
+  <si>
+    <t>アルバイトのとき、バイト先</t>
+  </si>
+  <si>
+    <t>subject</t>
+  </si>
+  <si>
+    <t>件名</t>
+  </si>
+  <si>
+    <t>sender</t>
+  </si>
+  <si>
+    <t>差出人</t>
+  </si>
+  <si>
+    <t>received_at</t>
+  </si>
+  <si>
+    <t>受け取った日時</t>
+  </si>
+  <si>
+    <t>body</t>
+  </si>
+  <si>
+    <t>本文。90日で消す(構想設計)</t>
+  </si>
+  <si>
+    <t>links</t>
+  </si>
+  <si>
+    <t>本文の中のリンク(一覧)</t>
+  </si>
+  <si>
+    <t>seen</t>
+  </si>
+  <si>
+    <t>連絡の画面で見たか(メールの既読とは別)</t>
+  </si>
+  <si>
+    <t>notices workbench からの質問とお知らせ</t>
+  </si>
+  <si>
+    <t>【表】連絡の画面の「workbench から」と「自動で完了」(Q14・Q21〜Q23)</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>画面の名前の質問・バイト先の質問・候補日・自動で完了</t>
+  </si>
+  <si>
+    <t>中身(候補日の一覧、もとになったものなど)</t>
+  </si>
+  <si>
+    <t>自動で完了のとき、そのタスク</t>
+  </si>
+  <si>
+    <t>answered</t>
+  </si>
+  <si>
+    <t>答えたか</t>
+  </si>
+  <si>
+    <t>出した日時</t>
+  </si>
+  <si>
+    <t>window_rules 画面の名前の決まり</t>
+  </si>
+  <si>
+    <t>【表】全自動の作業記録で覚えた組み合わせ(Q23)。ずっと残す</t>
+  </si>
+  <si>
+    <t>app</t>
+  </si>
+  <si>
+    <t>アプリ(VS Code・Chrome など)</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>画面の名前の決まり(フォルダ名・ページ名など)</t>
+  </si>
+  <si>
+    <t>入れ物。「記録しない」は空</t>
+  </si>
+  <si>
+    <t>ignore</t>
+  </si>
+  <si>
+    <t>記録しないか</t>
+  </si>
+  <si>
+    <t>pending_windows 答えを待つ画面の名前</t>
+  </si>
+  <si>
+    <t>【表】初めて見た画面の名前(Q23)。答えたら消す</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>画面の名前(個人的な文字が入ることがあるので、答えたら消す)</t>
+  </si>
+  <si>
+    <t>first_seen</t>
+  </si>
+  <si>
+    <t>初めて見た日時</t>
+  </si>
+  <si>
+    <t>sort_rules 振り分けの覚え</t>
+  </si>
+  <si>
+    <t>【表】選び直した結果(F9・F11)。ずっと残す</t>
+  </si>
+  <si>
+    <t>blocked_senders 止めた差出人</t>
+  </si>
+  <si>
+    <t>【表】[この差出人は取り込まない](Q20)</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>アドレス</t>
+  </si>
+  <si>
+    <t>止めた日時</t>
+  </si>
+  <si>
+    <t>deleted_items 消したものの記録</t>
+  </si>
+  <si>
+    <t>【表】自動で入って消したタスク・予定を、次に読んだときに戻さないため(F9)</t>
+  </si>
+  <si>
+    <t>もとのメールの番号</t>
+  </si>
+  <si>
+    <t>what</t>
+  </si>
+  <si>
+    <t>タスクか予定か</t>
+  </si>
+  <si>
+    <t>baito_places バイト先</t>
+  </si>
+  <si>
+    <t>【表】アルバイトの見分け(F20・Q21)</t>
+  </si>
+  <si>
+    <t>バイト先の名前</t>
+  </si>
+  <si>
+    <t>relay_address</t>
+  </si>
+  <si>
+    <t>覚えた中継アドレス(@ の前も全部)</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>直接送ってくるときの @ から後ろ</t>
+  </si>
+  <si>
+    <t>links リンク</t>
+  </si>
+  <si>
+    <t>【表】今日のリンク(Q27)</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>URL、または PC のアプリ・フォルダの場所</t>
+  </si>
+  <si>
+    <t>always_top</t>
+  </si>
+  <si>
+    <t>いつもトップに出すか</t>
+  </si>
+  <si>
+    <t>event_extras スケジュールの付け足し</t>
+  </si>
+  <si>
+    <t>【表】Google の予定ごとに workbench だけが持つもの(F19)。予定が Google から消えたら消す</t>
+  </si>
+  <si>
+    <t>google_event_id</t>
+  </si>
+  <si>
+    <t>Google の予定の番号</t>
+  </si>
+  <si>
+    <t>入っている入れ物</t>
+  </si>
+  <si>
+    <t>edit_allowed</t>
+  </si>
+  <si>
+    <t>招待された予定の編集を許すトグル</t>
+  </si>
+  <si>
+    <t>marked</t>
+  </si>
+  <si>
+    <t>workbench が書いた目印つきの予定か(F13)</t>
+  </si>
+  <si>
+    <t>締切の予定のとき、そのタスク</t>
+  </si>
+  <si>
+    <t>メールから入ったとき、もとの連絡</t>
+  </si>
+  <si>
+    <t>Claude が読み取ったか</t>
+  </si>
+  <si>
+    <t>held_events 預かった予定</t>
+  </si>
+  <si>
+    <t>【表】Google に書けなかった予定(F13)。書けたら、または「書かない」を選んだら消す</t>
+  </si>
+  <si>
+    <t>start_at</t>
+  </si>
+  <si>
+    <t>始まり(締切は終日)</t>
+  </si>
+  <si>
+    <t>end_at</t>
+  </si>
+  <si>
+    <t>終わり</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>つながらなかった/重なる予定がある</t>
+  </si>
+  <si>
+    <t>締切のとき、そのタスク</t>
+  </si>
+  <si>
+    <t>pending_pc_notices 出せなかった通知</t>
+  </si>
+  <si>
+    <t>【表】PC の電源が切れていた間の通知(F8)。見せたら消す</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>通知の中身</t>
+  </si>
+  <si>
+    <t>due_at</t>
+  </si>
+  <si>
+    <t>出すはずだった日時</t>
+  </si>
+  <si>
+    <t>claude_jobs Claude のやり直し</t>
+  </si>
+  <si>
+    <t>【表】Claude の読み取りの失敗とやり直し(Q6)</t>
+  </si>
+  <si>
+    <t>締切の読み取り・見分け・終わっていそう・候補日の判断など</t>
+  </si>
+  <si>
+    <t>何を読ませたか(連絡の番号など)</t>
+  </si>
+  <si>
+    <t>tries</t>
+  </si>
+  <si>
+    <t>やり直した回数(3回失敗したら2段目④)</t>
+  </si>
+  <si>
+    <t>next_try_at</t>
+  </si>
+  <si>
+    <t>次に試す日時</t>
+  </si>
+  <si>
+    <t>last_error</t>
+  </si>
+  <si>
+    <t>最後の失敗の中身</t>
+  </si>
+  <si>
+    <t>job_status 本体の様子</t>
+  </si>
+  <si>
+    <t>【表】裏の仕事ごとの最後に動いた時刻(Q19)</t>
+  </si>
+  <si>
+    <t>job</t>
+  </si>
+  <si>
+    <t>仕事の名前(Outlook・Gmail・Google カレンダー・通知・Claude・予備・作業記録)</t>
+  </si>
+  <si>
+    <t>last_run_at</t>
+  </si>
+  <si>
+    <t>最後に動いた日時</t>
+  </si>
+  <si>
+    <t>settings 設定</t>
+  </si>
+  <si>
+    <t>【表】1つずつの設定の値</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>設定の名前(大学のアドレスの形・シフト表での自分の名前・学期の終わりの日・1行入力の AI トグル)</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>トップの中身をまとめて読む(ゲージ・記録中・お知らせ・期限切れ・今日のリンク・今日と明日の時間・今日・今週・締切なし)</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>/api/top</t>
+  </si>
+  <si>
+    <t>S1-1〜S1-12</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>1行入力からタスクを作る</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/api/quick-input</t>
+  </si>
+  <si>
+    <t>AI トグルがオンのとき(F17)</t>
+  </si>
+  <si>
+    <t>S1-6・S5-3a</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>タスクを足す(くわしく)</t>
+  </si>
+  <si>
+    <t>/api/tasks</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>タスクを直す・完了にする・完了を外す</t>
+  </si>
+  <si>
+    <t>PATCH</t>
+  </si>
+  <si>
+    <t>/api/tasks/{id}</t>
+  </si>
+  <si>
+    <t>S1-8〜10・S5-3</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>タスクを消す</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>「AI」の札を確かめた</t>
+  </si>
+  <si>
+    <t>/api/tasks/{id}/ai-checked</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>「終わった?」に答える(入れ物の単位)</t>
+  </si>
+  <si>
+    <t>/api/done-questions/{id}</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>今の自動の記録を読む</t>
+  </si>
+  <si>
+    <t>/api/work-logs/current</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>作業記録を読む(入れ物ごと・日付ごと、コミットも)</t>
+  </si>
+  <si>
+    <t>/api/containers/{id}/logs</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>作業記録を直す・足す・消す</t>
+  </si>
+  <si>
+    <t>POST/PATCH/DELETE</t>
+  </si>
+  <si>
+    <t>/api/work-logs(/{id})</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>コミットを消す(次から取り込まない)</t>
+  </si>
+  <si>
+    <t>/api/commits/{id}</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>入れ物の一覧を読む(種類ごと・並び順・ゲージ・未分類の件数・終了したもの)</t>
+  </si>
+  <si>
+    <t>/api/containers</t>
+  </si>
+  <si>
+    <t>S4-1〜S4-4</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>入れ物を足す・直す・終了にする・戻す・消す</t>
+  </si>
+  <si>
+    <t>/api/containers(/{id})</t>
+  </si>
+  <si>
+    <t>S4-1・S4-4・S5-6</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>入れ物の中を読む(説明・工程・ゲージ・作業時間・タスク)</t>
+  </si>
+  <si>
+    <t>/api/containers/{id}</t>
+  </si>
+  <si>
+    <t>S5-1・S5-3</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>リンクを足す・直す・消す</t>
+  </si>
+  <si>
+    <t>/api/links(/{id})</t>
+  </si>
+  <si>
+    <t>A16</t>
+  </si>
+  <si>
+    <t>リンクを開く(PC のアプリ・フォルダは本体が開く)</t>
+  </si>
+  <si>
+    <t>/api/links/{id}/open</t>
+  </si>
+  <si>
+    <t>A17</t>
+  </si>
+  <si>
+    <t>スケジュールを読む(一覧・月。Google の予定・授業・締切)</t>
+  </si>
+  <si>
+    <t>/api/schedule?from=&amp;to=</t>
+  </si>
+  <si>
+    <t>S2-4・S2-4m</t>
+  </si>
+  <si>
+    <t>A18</t>
+  </si>
+  <si>
+    <t>予定を足す・直す・消す(その場で Google に書く)</t>
+  </si>
+  <si>
+    <t>/api/events(/{id})</t>
+  </si>
+  <si>
+    <t>S2-1a・S2-5</t>
+  </si>
+  <si>
+    <t>A19</t>
+  </si>
+  <si>
+    <t>Google に書けなかった予定を読む・もう一度書く・それでも書く・書かない</t>
+  </si>
+  <si>
+    <t>GET/POST</t>
+  </si>
+  <si>
+    <t>/api/held-events(/{id}/retry|force|drop)</t>
+  </si>
+  <si>
+    <t>A20</t>
+  </si>
+  <si>
+    <t>シフト表の写真を読み取る</t>
+  </si>
+  <si>
+    <t>/api/shift-photo</t>
+  </si>
+  <si>
+    <t>Claude(F14)</t>
+  </si>
+  <si>
+    <t>A21</t>
+  </si>
+  <si>
+    <t>シフト表の読み取り結果を書き込む</t>
+  </si>
+  <si>
+    <t>/api/shift-photo/commit</t>
+  </si>
+  <si>
+    <t>A22</t>
+  </si>
+  <si>
+    <t>連絡の分類と件数を読む(開いたら「見た」にする)</t>
+  </si>
+  <si>
+    <t>/api/messages/summary</t>
+  </si>
+  <si>
+    <t>S3-1・S1-4・S1-11</t>
+  </si>
+  <si>
+    <t>A23</t>
+  </si>
+  <si>
+    <t>分類ごとのメールの一覧・本文を読む</t>
+  </si>
+  <si>
+    <t>/api/messages?category= ・/api/messages/{id}</t>
+  </si>
+  <si>
+    <t>S3-3・S3-4</t>
+  </si>
+  <si>
+    <t>A24</t>
+  </si>
+  <si>
+    <t>メールの入れ物を選び直す(選び直しを覚える)</t>
+  </si>
+  <si>
+    <t>/api/messages/{id}</t>
+  </si>
+  <si>
+    <t>A25</t>
+  </si>
+  <si>
+    <t>差出人を止める・外す</t>
+  </si>
+  <si>
+    <t>POST/DELETE</t>
+  </si>
+  <si>
+    <t>/api/blocked-senders(/{id})</t>
+  </si>
+  <si>
+    <t>S3-4・S6-2</t>
+  </si>
+  <si>
+    <t>A26</t>
+  </si>
+  <si>
+    <t>workbench からの質問とお知らせを読む</t>
+  </si>
+  <si>
+    <t>/api/notices</t>
+  </si>
+  <si>
+    <t>A27</t>
+  </si>
+  <si>
+    <t>質問に答える(画面の名前・バイト先・候補日)</t>
+  </si>
+  <si>
+    <t>/api/notices/{id}/answer</t>
+  </si>
+  <si>
+    <t>A28</t>
+  </si>
+  <si>
+    <t>自動で完了の欄を読む・[戻す]</t>
+  </si>
+  <si>
+    <t>/api/auto-done(/{task_id}/undo)</t>
+  </si>
+  <si>
+    <t>A29</t>
+  </si>
+  <si>
+    <t>「終わっていそう」を読む・完了にする</t>
+  </si>
+  <si>
+    <t>/api/maybe-done(/{id})</t>
+  </si>
+  <si>
+    <t>Claude(1日1回の判断の結果を読む)</t>
+  </si>
+  <si>
+    <t>A30</t>
+  </si>
+  <si>
+    <t>設定を読む・直す(種類・大学・バイト先・画面の名前の決まり・学期の終わり・AI トグル)</t>
+  </si>
+  <si>
+    <t>GET/PATCH</t>
+  </si>
+  <si>
+    <t>/api/settings ・/api/kinds ・/api/baito ・/api/window-rules</t>
+  </si>
+  <si>
+    <t>S6-1〜S6-5</t>
+  </si>
+  <si>
+    <t>A31</t>
+  </si>
+  <si>
+    <t>Google の許可をし直す</t>
+  </si>
+  <si>
+    <t>/auth/google</t>
+  </si>
+  <si>
+    <t>A32</t>
+  </si>
+  <si>
+    <t>本体の様子を読む</t>
+  </si>
+  <si>
+    <t>/api/status</t>
+  </si>
+  <si>
+    <t>S6-6・S1-4</t>
+  </si>
+  <si>
+    <t>A33</t>
+  </si>
+  <si>
+    <t>学期の入れ替え(管理用の小さな命令。画面からは呼ばない)</t>
+  </si>
+  <si>
+    <t>―</t>
+  </si>
+  <si>
+    <t>python manage.py new-term</t>
+  </si>
+  <si>
+    <t>Claude(学年暦を読む。Q7)</t>
+  </si>
+  <si>
+    <t>Outlook が読めない(サインイン切れなど)</t>
+  </si>
+  <si>
+    <t>推測で埋めない。2段目④に「大学のメールを読めませんでした」。10分後にまた試す(F9)</t>
+  </si>
+  <si>
+    <t>Gmail が読めない(許可切れなど)</t>
+  </si>
+  <si>
+    <t>2段目④に「Gmail を読めませんでした」。許可切れのときは設定の [許可し直す] へのつながりを出す(F11・S6-3)</t>
+  </si>
+  <si>
+    <t>Google カレンダーに書けない</t>
+  </si>
+  <si>
+    <t>預かった予定に残し、S2-3 の帯に出す。つながったら自動で書く。[もう一度書く] で手でも試せる。重なる予定のときは [それでも書く] [書かない](F13・S2-3)</t>
+  </si>
+  <si>
+    <t>Google カレンダーが読めない</t>
+  </si>
+  <si>
+    <t>前に読んだ予定は出さない(写しを持たないため)。スケジュールの画面に「Google に接続できませんでした」と出し、足す・直すはできない(F19)</t>
+  </si>
+  <si>
+    <t>Claude の読み取りの失敗</t>
+  </si>
+  <si>
+    <t>自動でやり直し、3回失敗したら2段目④。シフト表の写真はすぐ小窓に出す。終わっていそうは次の日にやり直す(Q6)。失敗の記録は claude_jobs に残す</t>
+  </si>
+  <si>
+    <t>1行入力が読み取れない</t>
+  </si>
+  <si>
+    <t>その場でタスクにする。入れ物が読めなければ未分類と印、締切が読めなければ締切なし(F17)</t>
+  </si>
+  <si>
+    <t>git の取り込みの失敗(リポジトリが見つからないなど)</t>
+  </si>
+  <si>
+    <t>2段目④に「○○のリポジトリを読めませんでした」。入れ物の設定でリポジトリの場所を直せる(F7)</t>
+  </si>
+  <si>
+    <t>画面の名前が読めない(PC が眠っている・ロック中)</t>
+  </si>
+  <si>
+    <t>その間は記録しない。眠った時刻で記録を止める(F4・Q25)</t>
+  </si>
+  <si>
+    <t>裏の仕事が止まっている</t>
+  </si>
+  <si>
+    <t>本体の様子で赤く出し、2段目④に「止まっている仕事があります」。遅れの目安(Claude の案):メール・カレンダーは30分、作業記録は5分、予備は1日、Claude は1日(Q19)</t>
+  </si>
+  <si>
+    <t>本体そのものが止まっている</t>
+  </si>
+  <si>
+    <t>タスクスケジューラが立ち上げ直す(構想設計)。画面が開けないときのために、手で起動する .bat を置く(Claude の案)</t>
+  </si>
+  <si>
+    <t>データの保存に失敗した</t>
+  </si>
+  <si>
+    <t>画面の入力は消さずに残し、「保存できませんでした。もう一度押してください」と出す(Claude の案)</t>
+  </si>
+  <si>
+    <t>データのファイルが壊れた</t>
+  </si>
+  <si>
+    <t>毎日の予備(7日分)から戻す。戻し方は README に書く(Q17)</t>
+  </si>
+  <si>
+    <t>消す操作</t>
+  </si>
+  <si>
+    <t>タスク・作業記録・予定・入れ物を消す前は確認を出す。トップの完了は5秒間「元に戻す」(F2・F5・F19・画面2)</t>
+  </si>
+  <si>
+    <t>Claude Code の使用量の上限に達した</t>
+  </si>
+  <si>
+    <t>上限に達したら、Claude を使う仕事をまとめて止め、2段目に「Claude の使用量の上限のため、○時まで読み取りを止めています」と出す。止めている間の分は claude_jobs にためておき、解けたら自動で続ける。上限で止まった分は、やり直しの回数(3回)に数えない(エラー1)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>呼び方(全部に共通)</t>
+  </si>
+  <si>
+    <t>claude -p(Claude Code。追加の費用なし。C1)を本体の裏から呼ぶ。答えは必ず JSON の形で返させ、形が崩れていたら失敗として扱う(Q6・エラー1)。渡すのは、その仕事に要るものだけにする</t>
+  </si>
+  <si>
+    <t>① 締切・面接日の読み取り(F9・F11・F20)</t>
+  </si>
+  <si>
+    <t>渡すもの:件名・本文・受け取った日。決まった書き方で見つからず、「締切」「〆切」「期限」「提出」「面接」「面談」のどれかがあるメールだけ。返させる形:{"items":[{"kind":"締切|日時","date":"YYYY-MM-DD","time":"HH:MM|null","title":"…"}]}。崩れたら:やり直し3回 → 2段目④</t>
+  </si>
+  <si>
+    <t>② 面接の候補日か決定かの判断(Q22)</t>
+  </si>
+  <si>
+    <t>渡すもの:日時が書いてある企業・アルバイトのメールの本文。返させる形:{"type":"決定|候補|不明","dates":[{"date":…,"start":…,"end":…}]}。「不明」と崩れたときは候補日と同じ扱い(ボタンで選ぶ)</t>
+  </si>
+  <si>
+    <t>③ メール・コミットとタスクの見分け(Q12・Q13)</t>
+  </si>
+  <si>
+    <t>渡すもの:件名(またはコミットのメッセージ)と、まだ終わっていないタスクの一覧(番号・名前・入れ物・締切)。企業は、その企業の入れ物のタスクだけ。返させる形:{"task_id":番号|null}。null か、一覧にない番号が返ったら完了にせず「終わっていそう」に回す</t>
+  </si>
+  <si>
+    <t>④ 終わっていそうの判断(F18 ④)</t>
+  </si>
+  <si>
+    <t>1日1回、その日最初に PC を使い始めたとき。渡すもの:前回から後のメールの件名・コミット・作業記録の合計と、未完了のタスクの一覧。返させる形:{"maybe_done":[{"task_id":…,"reason":"…"}]}。失敗したら次の日にやり直す(Q6)</t>
+  </si>
+  <si>
+    <t>⑤ 1行入力の読み取り(F17・Q10)</t>
+  </si>
+  <si>
+    <t>AI トグルがオンのときだけ。渡すもの:打った文字・今日の日付・入れ物の名前の一覧。返させる形:{"title":…,"date":…|null,"time":…|null,"container_id":…|null}。失敗したら決まった書き方で読み直す</t>
+  </si>
+  <si>
+    <t>⑥ シフト表の写真(F14)</t>
+  </si>
+  <si>
+    <t>渡すもの:写真と、シフト表での自分の名前。返させる形:{"shifts":[{"date":…,"start":…,"end":…}]}。結果は小窓に出し、[書き込む] を押したら予定にする。写真と結果は残さない。失敗したらすぐ小窓に出す(Q6)</t>
+  </si>
+  <si>
+    <t>⑦ 学期の終わりの日(F10・Q7)</t>
+  </si>
+  <si>
+    <t>管理用の小さな命令から呼ぶ。渡すもの:大学の学年暦の PDF の文字。返させる形:{"term_end":"YYYY-MM-DD"}。結果は設定の「学期の終わりの日」に入れ、画面で直せる</t>
+  </si>
+  <si>
+    <t>Claude に渡さないもの</t>
+  </si>
+  <si>
+    <t>作業記録の画面の名前(Q23 は自分で答える)。大学のアドレスの形など data/ の設定。Google の鍵</t>
   </si>
 </sst>
 </file>
@@ -1192,7 +2345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1222,6 +2375,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2155,114 +3311,114 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="54">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="16" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="108">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="108">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="18" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="121.5">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="108">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="18" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="94.5">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="18" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="67.5">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="18" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="67.5">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2322,618 +3478,618 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="27">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="18" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="40.5">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="18" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="54">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="18" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="27">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="18" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="18" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="18" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="40.5">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="18" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="18" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="18" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="40.5">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="18" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="27">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="18" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="40.5">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="18" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="18" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="54">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="18" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="40.5">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="18" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="27">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="18" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="40.5">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="40.5">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="18" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="54">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="18" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="27">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="18" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="40.5">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="18" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="27">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="18" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="27">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="54">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="18" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="18" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="40.5">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="18" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="18" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="27">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>276</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="18" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="27">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="18" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="27">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="18" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="40.5">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="18" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="40.5">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="18" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="18" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="40.5">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="18" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="40.5">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>304</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="18" t="s">
         <v>305</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="18" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="18" t="s">
         <v>309</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="18" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="27">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="18" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="27">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="18" t="s">
         <v>317</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="18" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="40.5">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="18" t="s">
         <v>319</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="18" t="s">
         <v>322</v>
       </c>
     </row>
@@ -2952,7 +4108,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2996,6 +4152,1954 @@
       </c>
       <c r="E5" s="6" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="27">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="27">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="27">
+      <c r="A42" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="27">
+      <c r="A58" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E60" s="18" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18" t="s">
+        <v>423</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="40.5">
+      <c r="A71" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E72" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E76" s="18" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="27">
+      <c r="A78" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18" t="s">
+        <v>453</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="18"/>
+      <c r="B82" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="18"/>
+      <c r="B83" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="40.5">
+      <c r="A84" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="18"/>
+      <c r="B85" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="18"/>
+      <c r="B86" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D86" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E86" s="18" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="18"/>
+      <c r="B87" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="27">
+      <c r="A88" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="18"/>
+      <c r="B89" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="18"/>
+      <c r="B90" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="18"/>
+      <c r="B91" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D91" s="18"/>
+      <c r="E91" s="18" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="18"/>
+      <c r="B92" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="27">
+      <c r="A93" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="18"/>
+      <c r="B94" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C94" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="18"/>
+      <c r="B95" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="C95" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E95" s="18" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="18"/>
+      <c r="B96" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="27">
+      <c r="A97" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="18" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="18"/>
+      <c r="B98" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C98" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D98" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="18"/>
+      <c r="B99" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="C99" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D99" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E99" s="18" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="18"/>
+      <c r="B100" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="C100" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="27">
+      <c r="A101" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="B101" s="18"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="18" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="18"/>
+      <c r="B102" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C102" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="18"/>
+      <c r="B103" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C103" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E103" s="18" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="18"/>
+      <c r="B104" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D104" s="18"/>
+      <c r="E104" s="18" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="18"/>
+      <c r="B105" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="C105" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D105" s="18"/>
+      <c r="E105" s="18" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="B106" s="18"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="18"/>
+      <c r="E106" s="18" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="18"/>
+      <c r="B107" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C107" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D107" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E107" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="18"/>
+      <c r="B108" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C108" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D108" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E108" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="18"/>
+      <c r="B109" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C109" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D109" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E109" s="18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="18"/>
+      <c r="B110" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="C110" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E110" s="18" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="18"/>
+      <c r="B111" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="C111" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D111" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E111" s="18" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="40.5">
+      <c r="A112" s="18" t="s">
+        <v>489</v>
+      </c>
+      <c r="B112" s="18"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="18"/>
+      <c r="B113" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D113" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E113" s="18" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="18"/>
+      <c r="B114" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C114" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="18"/>
+      <c r="B115" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="C115" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D115" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E115" s="18" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="18"/>
+      <c r="B116" s="18" t="s">
+        <v>496</v>
+      </c>
+      <c r="C116" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D116" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E116" s="18" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="18"/>
+      <c r="B117" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="C117" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D117" s="18"/>
+      <c r="E117" s="18" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="18"/>
+      <c r="B118" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="C118" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D118" s="18"/>
+      <c r="E118" s="18" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="18"/>
+      <c r="B119" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="C119" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E119" s="18" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="27">
+      <c r="A120" s="18" t="s">
+        <v>501</v>
+      </c>
+      <c r="B120" s="18"/>
+      <c r="C120" s="18"/>
+      <c r="D120" s="18"/>
+      <c r="E120" s="18" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="18"/>
+      <c r="B121" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C121" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E121" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="18"/>
+      <c r="B122" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="C122" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E122" s="18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="18"/>
+      <c r="B123" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="C123" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D123" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E123" s="18" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="18"/>
+      <c r="B124" s="18" t="s">
+        <v>505</v>
+      </c>
+      <c r="C124" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D124" s="18"/>
+      <c r="E124" s="18" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="18"/>
+      <c r="B125" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="C125" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E125" s="18" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="18"/>
+      <c r="B126" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="C126" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D126" s="18"/>
+      <c r="E126" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="18"/>
+      <c r="B127" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="C127" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D127" s="18"/>
+      <c r="E127" s="18" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="27">
+      <c r="A128" s="18" t="s">
+        <v>510</v>
+      </c>
+      <c r="B128" s="18"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="18"/>
+      <c r="E128" s="18" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="18"/>
+      <c r="B129" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C129" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D129" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E129" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="18"/>
+      <c r="B130" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C130" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D130" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E130" s="18" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="18"/>
+      <c r="B131" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="C131" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D131" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E131" s="18" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="27">
+      <c r="A132" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="B132" s="18"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="18"/>
+      <c r="B133" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="C133" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E133" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="18"/>
+      <c r="B134" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="C134" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D134" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E134" s="18" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="18"/>
+      <c r="B135" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D135" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E135" s="18" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="18"/>
+      <c r="B136" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="C136" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D136" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E136" s="18" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="18"/>
+      <c r="B137" s="18" t="s">
+        <v>522</v>
+      </c>
+      <c r="C137" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D137" s="18"/>
+      <c r="E137" s="18" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="18"/>
+      <c r="B138" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="C138" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D138" s="18"/>
+      <c r="E138" s="18" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="27">
+      <c r="A139" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="27">
+      <c r="A140" s="18"/>
+      <c r="B140" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="C140" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E140" s="18" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="18"/>
+      <c r="B141" s="18" t="s">
+        <v>530</v>
+      </c>
+      <c r="C141" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D141" s="18"/>
+      <c r="E141" s="18" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="18"/>
+      <c r="B142" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="C142" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D142" s="18"/>
+      <c r="E142" s="18" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="18" t="s">
+        <v>532</v>
+      </c>
+      <c r="B143" s="18"/>
+      <c r="C143" s="18"/>
+      <c r="D143" s="18"/>
+      <c r="E143" s="18" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="27">
+      <c r="A144" s="18"/>
+      <c r="B144" s="18" t="s">
+        <v>534</v>
+      </c>
+      <c r="C144" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D144" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E144" s="18" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="18"/>
+      <c r="B145" s="18" t="s">
+        <v>536</v>
+      </c>
+      <c r="C145" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="E145" s="18" t="s">
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -3013,7 +6117,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3062,6 +6166,608 @@
       </c>
       <c r="F5" s="6" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="54">
+      <c r="A6" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="40.5">
+      <c r="A7" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>544</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>547</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>551</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="27">
+      <c r="A9" s="18" t="s">
+        <v>552</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>558</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="18" t="s">
+        <v>560</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>561</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>562</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="18" t="s">
+        <v>563</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>564</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>565</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="18" t="s">
+        <v>566</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>567</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>568</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="27">
+      <c r="A14" s="18" t="s">
+        <v>569</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>570</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>571</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="40.5">
+      <c r="A15" s="18" t="s">
+        <v>572</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>573</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>574</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="18" t="s">
+        <v>576</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>577</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>578</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="40.5">
+      <c r="A17" s="18" t="s">
+        <v>579</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>580</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>581</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="40.5">
+      <c r="A18" s="18" t="s">
+        <v>583</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>584</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>574</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>585</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="27">
+      <c r="A19" s="18" t="s">
+        <v>587</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>588</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>589</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="40.5">
+      <c r="A20" s="18" t="s">
+        <v>591</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>592</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>574</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>593</v>
+      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="27">
+      <c r="A21" s="18" t="s">
+        <v>594</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>595</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="27">
+      <c r="A22" s="18" t="s">
+        <v>597</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>598</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>599</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="40.5">
+      <c r="A23" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>602</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>574</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>603</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="27">
+      <c r="A24" s="18" t="s">
+        <v>605</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>606</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>608</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="27">
+      <c r="A25" s="18" t="s">
+        <v>609</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>610</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>611</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>612</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>614</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>615</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="27">
+      <c r="A27" s="18" t="s">
+        <v>616</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>618</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="27">
+      <c r="A28" s="18" t="s">
+        <v>620</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>621</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>622</v>
+      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="27">
+      <c r="A29" s="18" t="s">
+        <v>624</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>625</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>626</v>
+      </c>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="27">
+      <c r="A30" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>628</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>629</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>630</v>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="27">
+      <c r="A31" s="18" t="s">
+        <v>632</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>633</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>634</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="27">
+      <c r="A32" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>636</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>545</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>637</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="18" t="s">
+        <v>638</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>639</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>640</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="54">
+      <c r="A34" s="18" t="s">
+        <v>641</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>642</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>643</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>644</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="40.5">
+      <c r="A35" s="18" t="s">
+        <v>645</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>646</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>648</v>
+      </c>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="18" t="s">
+        <v>650</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>651</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>652</v>
+      </c>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="18" t="s">
+        <v>653</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>654</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>655</v>
+      </c>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="40.5">
+      <c r="A38" s="18" t="s">
+        <v>657</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>658</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>659</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>660</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>661</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -3079,7 +6785,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3108,6 +6814,118 @@
       </c>
       <c r="B5" s="6" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="27">
+      <c r="A6" s="16" t="s">
+        <v>662</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="27">
+      <c r="A7" s="18" t="s">
+        <v>664</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="27">
+      <c r="A8" s="18" t="s">
+        <v>666</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="27">
+      <c r="A9" s="18" t="s">
+        <v>668</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="27">
+      <c r="A10" s="18" t="s">
+        <v>670</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="27">
+      <c r="A12" s="18" t="s">
+        <v>674</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="27">
+      <c r="A13" s="18" t="s">
+        <v>676</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="27">
+      <c r="A14" s="18" t="s">
+        <v>678</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="27">
+      <c r="A15" s="18" t="s">
+        <v>680</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="18" t="s">
+        <v>682</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="18" t="s">
+        <v>684</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="27">
+      <c r="A18" s="18" t="s">
+        <v>686</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="40.5">
+      <c r="A19" s="18" t="s">
+        <v>688</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -3125,7 +6943,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3156,6 +6974,78 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:2" ht="27">
+      <c r="A6" s="15" t="s">
+        <v>690</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="40.5">
+      <c r="A7" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="27">
+      <c r="A8" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="40.5">
+      <c r="A9" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="40.5">
+      <c r="A10" s="17" t="s">
+        <v>698</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="40.5">
+      <c r="A11" s="17" t="s">
+        <v>700</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="40.5">
+      <c r="A12" s="17" t="s">
+        <v>702</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="27">
+      <c r="A13" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="17" t="s">
+        <v>706</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>707</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
